--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2025.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2025.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:T201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -593,6 +603,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -679,6 +699,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -765,6 +795,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -851,6 +891,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -937,6 +987,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1023,6 +1083,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1109,6 +1179,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1195,6 +1275,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1281,6 +1371,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1367,6 +1467,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1453,6 +1563,16 @@
           <t>150128</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1539,6 +1659,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1625,6 +1755,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1711,6 +1851,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1797,6 +1947,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1883,6 +2043,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1969,6 +2139,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2055,6 +2235,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2143,6 +2333,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2231,6 +2431,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2319,6 +2529,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2405,6 +2625,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2491,6 +2721,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2579,6 +2819,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2667,6 +2917,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2755,6 +3015,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2843,6 +3113,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2931,6 +3211,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3019,6 +3309,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3107,6 +3407,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3195,6 +3505,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3283,6 +3603,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3371,6 +3701,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3457,6 +3797,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3545,6 +3895,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3633,6 +3993,16 @@
           <t>150133</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3719,6 +4089,16 @@
           <t>150133</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3807,6 +4187,16 @@
           <t>150133</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3895,6 +4285,16 @@
           <t>150133</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3981,6 +4381,16 @@
           <t>150133</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4069,6 +4479,16 @@
           <t>150119</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4155,6 +4575,16 @@
           <t>150123</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4243,6 +4673,16 @@
           <t>150123</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4331,6 +4771,16 @@
           <t>150123</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4419,6 +4869,16 @@
           <t>150124</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4507,6 +4967,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4595,6 +5065,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4683,6 +5163,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4771,6 +5261,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4859,6 +5359,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4945,6 +5455,16 @@
           <t>150102</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5033,6 +5553,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5121,6 +5651,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5209,6 +5749,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5295,6 +5845,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5383,6 +5943,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5469,6 +6039,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5557,6 +6137,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5643,6 +6233,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5731,6 +6331,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5819,6 +6429,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5907,6 +6527,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5993,6 +6623,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6081,6 +6721,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6169,6 +6819,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6257,6 +6917,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6345,6 +7015,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6433,6 +7113,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6521,6 +7211,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6607,6 +7307,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6695,6 +7405,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6783,6 +7503,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6871,6 +7601,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6959,6 +7699,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7047,6 +7797,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7135,6 +7895,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7221,6 +7991,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7309,6 +8089,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7397,6 +8187,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7485,6 +8285,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7571,6 +8381,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7659,6 +8479,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7747,6 +8577,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7835,6 +8675,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7923,6 +8773,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -8011,6 +8871,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -8099,6 +8969,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -8187,6 +9067,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -8275,6 +9165,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -8363,6 +9263,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8449,6 +9359,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -8537,6 +9457,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8625,6 +9555,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8711,6 +9651,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8797,6 +9747,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8885,6 +9845,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8973,6 +9943,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -9061,6 +10041,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -9147,6 +10137,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -9235,6 +10235,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -9323,6 +10333,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -9411,6 +10431,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -9499,6 +10529,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -9587,6 +10627,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -9675,6 +10725,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -9763,6 +10823,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -9849,6 +10919,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -9935,6 +11015,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -10023,6 +11113,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -10109,6 +11209,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -10195,6 +11305,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -10283,6 +11403,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -10371,6 +11501,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -10459,6 +11599,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -10545,6 +11695,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -10633,6 +11793,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -10721,6 +11891,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -10809,6 +11989,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -10897,6 +12087,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -10985,6 +12185,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -11073,6 +12283,16 @@
           <t>150111</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -11161,6 +12381,16 @@
           <t>150111</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -11249,6 +12479,16 @@
           <t>150111</t>
         </is>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -11337,6 +12577,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -11425,6 +12675,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -11513,6 +12773,16 @@
           <t>150111</t>
         </is>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -11601,6 +12871,16 @@
           <t>150111</t>
         </is>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -11689,6 +12969,16 @@
           <t>150111</t>
         </is>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -11777,6 +13067,16 @@
           <t>150111</t>
         </is>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -11865,6 +13165,16 @@
           <t>150134</t>
         </is>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -11953,6 +13263,16 @@
           <t>150128</t>
         </is>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -12041,6 +13361,16 @@
           <t>150128</t>
         </is>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -12127,6 +13457,16 @@
           <t>150128</t>
         </is>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -12215,6 +13555,16 @@
           <t>150128</t>
         </is>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -12303,6 +13653,16 @@
           <t>150128</t>
         </is>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -12391,6 +13751,16 @@
           <t>150107</t>
         </is>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -12479,6 +13849,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -12567,6 +13947,16 @@
           <t>150107</t>
         </is>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -12655,6 +14045,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -12741,6 +14141,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -12829,6 +14239,16 @@
           <t>150115</t>
         </is>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -12917,6 +14337,16 @@
           <t>150115</t>
         </is>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -13005,6 +14435,16 @@
           <t>150115</t>
         </is>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -13093,6 +14533,16 @@
           <t>150115</t>
         </is>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -13181,6 +14631,16 @@
           <t>150116</t>
         </is>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -13269,6 +14729,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -13357,6 +14827,16 @@
           <t>150115</t>
         </is>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -13445,6 +14925,16 @@
           <t>150115</t>
         </is>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -13533,6 +15023,16 @@
           <t>150115</t>
         </is>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -13621,6 +15121,16 @@
           <t>150115</t>
         </is>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -13709,6 +15219,16 @@
           <t>150105</t>
         </is>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -13797,6 +15317,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -13885,6 +15415,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -13971,6 +15511,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -14059,6 +15609,16 @@
           <t>150136</t>
         </is>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -14147,6 +15707,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -14235,6 +15805,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -14323,6 +15903,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -14411,6 +16001,16 @@
           <t>150136</t>
         </is>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -14499,6 +16099,16 @@
           <t>150136</t>
         </is>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -14587,6 +16197,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -14675,6 +16295,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -14763,6 +16393,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -14851,6 +16491,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -14939,6 +16589,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -15025,6 +16685,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -15113,6 +16783,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -15201,6 +16881,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -15289,6 +16979,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -15377,6 +17077,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -15465,6 +17175,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -15553,6 +17273,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -15641,6 +17371,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -15729,6 +17469,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -15817,6 +17567,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -15903,6 +17663,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -15989,6 +17759,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -16075,6 +17855,16 @@
       <c r="R179" t="inlineStr">
         <is>
           <t>070106</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
         </is>
       </c>
     </row>
@@ -16145,6 +17935,8 @@
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -16231,6 +18023,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -16319,6 +18121,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -16405,6 +18217,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -16491,6 +18313,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -16577,6 +18409,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -16663,6 +18505,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -16751,6 +18603,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -16839,6 +18701,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -16927,6 +18799,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -17015,6 +18897,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -17103,6 +18995,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -17191,6 +19093,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -17279,6 +19191,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -17367,6 +19289,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -17455,6 +19387,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -17543,6 +19485,16 @@
           <t>070103</t>
         </is>
       </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -17631,6 +19583,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -17719,6 +19681,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -17807,6 +19779,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -17895,6 +19877,16 @@
           <t>070101</t>
         </is>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -17981,6 +19973,16 @@
       <c r="R201" t="inlineStr">
         <is>
           <t>070101</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2025.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2025.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T201"/>
+  <dimension ref="A1:U201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -613,6 +618,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -709,6 +719,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -805,6 +820,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -901,6 +921,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -997,6 +1022,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1093,6 +1123,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1189,6 +1224,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1285,6 +1325,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1381,6 +1426,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1477,6 +1527,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1573,6 +1628,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1669,6 +1729,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1765,6 +1830,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1861,6 +1931,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1957,6 +2032,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2053,6 +2133,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2149,6 +2234,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2245,6 +2335,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2343,6 +2438,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2441,6 +2541,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2539,6 +2644,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2635,6 +2745,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2731,6 +2846,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2829,6 +2949,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2927,6 +3052,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3025,6 +3155,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3123,6 +3258,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3221,6 +3361,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3319,6 +3464,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3417,6 +3567,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3515,6 +3670,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3613,6 +3773,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3711,6 +3876,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3807,6 +3977,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3905,6 +4080,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4003,6 +4183,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4099,6 +4284,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4197,6 +4387,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4295,6 +4490,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4391,6 +4591,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4489,6 +4694,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4585,6 +4795,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4683,6 +4898,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4781,6 +5001,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4879,6 +5104,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4977,6 +5207,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5075,6 +5310,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5173,6 +5413,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5271,6 +5516,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5369,6 +5619,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5465,6 +5720,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5563,6 +5823,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5661,6 +5926,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5759,6 +6029,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5855,6 +6130,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5953,6 +6233,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6049,6 +6334,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6147,6 +6437,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6243,6 +6538,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6341,6 +6641,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6439,6 +6744,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6537,6 +6847,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6633,6 +6948,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6731,6 +7051,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6829,6 +7154,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6927,6 +7257,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7025,6 +7360,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7123,6 +7463,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7221,6 +7566,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7317,6 +7667,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7415,6 +7770,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7513,6 +7873,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7611,6 +7976,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7709,6 +8079,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7807,6 +8182,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7905,6 +8285,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8001,6 +8386,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8099,6 +8489,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8197,6 +8592,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8295,6 +8695,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8391,6 +8796,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8489,6 +8899,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8587,6 +9002,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8685,6 +9105,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8783,6 +9208,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -8881,6 +9311,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -8979,6 +9414,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9077,6 +9517,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9175,6 +9620,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9273,6 +9723,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9369,6 +9824,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9467,6 +9927,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9565,6 +10030,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9661,6 +10131,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9757,6 +10232,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9855,6 +10335,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -9953,6 +10438,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10051,6 +10541,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10147,6 +10642,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10245,6 +10745,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10343,6 +10848,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10441,6 +10951,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10539,6 +11054,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10637,6 +11157,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10735,6 +11260,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10833,6 +11363,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -10929,6 +11464,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11025,6 +11565,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11123,6 +11668,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11219,6 +11769,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11315,6 +11870,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11413,6 +11973,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11511,6 +12076,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11609,6 +12179,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11705,6 +12280,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11803,6 +12383,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -11901,6 +12486,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -11999,6 +12589,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12097,6 +12692,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12195,6 +12795,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12293,6 +12898,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12391,6 +13001,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12489,6 +13104,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12587,6 +13207,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12685,6 +13310,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12783,6 +13413,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -12881,6 +13516,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -12979,6 +13619,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13077,6 +13722,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13175,6 +13825,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13273,6 +13928,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13371,6 +14031,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13467,6 +14132,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13565,6 +14235,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13663,6 +14338,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13761,6 +14441,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -13859,6 +14544,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -13957,6 +14647,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14055,6 +14750,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14151,6 +14851,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14249,6 +14954,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14347,6 +15057,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14445,6 +15160,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14543,6 +15263,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14641,6 +15366,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14739,6 +15469,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -14837,6 +15572,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -14935,6 +15675,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15033,6 +15778,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15131,6 +15881,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15229,6 +15984,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15327,6 +16087,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15425,6 +16190,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15521,6 +16291,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15619,6 +16394,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15717,6 +16497,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -15815,6 +16600,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -15913,6 +16703,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16011,6 +16806,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16109,6 +16909,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16207,6 +17012,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16305,6 +17115,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16403,6 +17218,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16501,6 +17321,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16599,6 +17424,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16695,6 +17525,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -16793,6 +17628,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -16891,6 +17731,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -16989,6 +17834,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17087,6 +17937,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17185,6 +18040,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17283,6 +18143,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17381,6 +18246,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17479,6 +18349,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -17577,6 +18452,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -17673,6 +18553,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -17769,6 +18654,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -17867,6 +18757,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -17930,13 +18825,42 @@
           <t>916351</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>VENTANILLA</t>
+        </is>
+      </c>
       <c r="Q180" t="inlineStr"/>
-      <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
-      <c r="T180" t="inlineStr"/>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>070106</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18033,6 +18957,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18131,6 +19060,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18227,6 +19161,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18323,6 +19262,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18419,6 +19363,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -18515,6 +19464,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -18613,6 +19567,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -18711,6 +19670,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -18809,6 +19773,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -18907,6 +19876,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19005,6 +19979,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19103,6 +20082,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19201,6 +20185,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19299,6 +20288,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19397,6 +20391,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -19495,6 +20494,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -19593,6 +20597,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -19691,6 +20700,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -19789,6 +20803,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -19887,6 +20906,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -19983,6 +21007,11 @@
       <c r="T201" t="inlineStr">
         <is>
           <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2025.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2025.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U201"/>
+  <dimension ref="A1:W201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -620,6 +630,16 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>INDEPENDENCIA/INDEPENDENCIA/INDEPENDENCIA/INDEPENDENCIA/INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -721,6 +741,16 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>0037 SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -822,6 +852,16 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>170 SANTA ROSA DEL SAUCE/170 SANTA ROSA DEL SAUCE/170 SANTA ROSA DEL SAUCE</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -923,6 +963,16 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>1173 JULIO CESAR TELLO/1173 JULIO CESAR TELLO/1173 JULIO CESAR TELLO/1173 JULIO CESAR TELLO/1173 JULIO CESAR TELLO</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1024,6 +1074,16 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>0043 JUAN PABLO II</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1125,6 +1185,16 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>PILOTO MADRE TERESA DE CALCUTA/PILOTO MADRE TERESA DE CALCUTA/168 AMISTAD PERU JAPON/168 AMISTAD PERU JAPON</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1226,6 +1296,16 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>035 ISABEL FLORES DE OLIVA</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1327,6 +1407,16 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>115-16 VIRGEN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1428,6 +1518,16 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>0087 JOSE MARIA ARGUEDAS/0087 JOSE MARIA ARGUEDAS/0087 JOSE MARIA ARGUEDAS</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1529,6 +1629,16 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>0092 ALFRED NOBEL/0092 ALFRED NOBEL/0092 ALFRED NOBEL</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1630,6 +1740,16 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>3015 LOS ANGELES DE JESUS/3015 LOS ANGELES DE JESUS/3015 LOS ANGELES DE JESUS</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1731,6 +1851,16 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>0115-26 EMILIA BARCIA BONIFFATTI</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1832,6 +1962,16 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>0045 SAN ANTONIO/0045 SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1933,6 +2073,16 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
+          <t>0115 25 CUNA DE JESUS</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2034,6 +2184,16 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
+          <t>0158 SANTA MARIA/0158 SANTA MARIA/0158 SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2135,6 +2295,16 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
+          <t>154 LOS CLAVELES</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2236,6 +2406,16 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
+          <t>0079 CUNA JARDIN</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2337,6 +2517,16 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2440,6 +2630,16 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>0111</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2543,6 +2743,16 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
+          <t>123 LOS ARBOLES/123 LOS ARBOLES</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2646,6 +2856,16 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
+          <t>136 SANTA ROSA MILAGROSA/136 SANTA ROSA MILAGROSA/136 SANTA ROSA MILAGROSA</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2747,6 +2967,16 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>144/0144</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2848,6 +3078,16 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
+          <t>0092</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2951,6 +3191,16 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
+          <t>117 SIGNOS DE FE/117 SIGNOS DE FE/117 SIGNOS DE FE</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3054,6 +3304,16 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
+          <t>116 ABRAHAM VALDELOMAR/116 ABRAHAM VALDELOMAR/116 ABRAHAM VALDELOMAR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3157,6 +3417,16 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
+          <t>6039 FERNANDO CARBAJAL SEGURA/6039 FERNANDO CARBAJAL SEGURA/6039 FERNANDO CARBAJAL SEGURA/6039 FERNANDO CARBAJAL SEGURA/6039 FERNANDO CARBAJAL SEGURA</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3260,6 +3530,16 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
+          <t>0032 RAUL PORRAS BARRENECHEA/0032 RAUL PORRAS BARRENECHEA</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3363,6 +3643,16 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>500 EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3466,6 +3756,16 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
+          <t>1136 JOHN F. KENNEDY/1136 JOHN F. KENNEDY/1136 JOHN F. KENNEDY/1136 JOHN F. KENNEDY</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3569,6 +3869,16 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
+          <t>0074 FERNANDO BELAUNDE TERRY/0074 FERNANDO BELAUNDE TERRY</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3672,6 +3982,16 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
+          <t>1252 SANTA ISABEL/1252 SANTA ISABEL</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3775,6 +4095,16 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
+          <t>1283 OKINAWA/1283 OKINAWA</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3878,6 +4208,16 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3979,6 +4319,16 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4082,6 +4432,16 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
+          <t>171 VIRGEN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4185,6 +4545,16 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>7100 REPUBLICA ALEMANA/7100 REPUBLICA ALEMANA/7100 REPUBLICA ALEMANA</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4286,6 +4656,16 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
+          <t>7211</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4389,6 +4769,16 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
+          <t>7060 ANDRES AVELINO CACERES/7060 ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4492,6 +4882,16 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
+          <t>7099 HECTOR PRETELL/7099 HECTOR PRETELL CARBONELL/7099 HECTOR PRETELL CARBONELL</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4593,6 +4993,16 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
+          <t>7209/7209</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4696,6 +5106,16 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
+          <t>657 EMILIA BARCIA BONIFATTI</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4797,6 +5217,16 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4900,6 +5330,16 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
+          <t>7263 ROXANITA CASTRO WITTING/668 ROXANITA CASTRO WITTING</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5003,6 +5443,16 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
+          <t>7259 VICTOR R. HAYA DE LA TORRE/7259 VICTOR R. HAYA DE LA TORRE/656 MI PEQUEÑO MUNDO</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5106,6 +5556,16 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
+          <t>550 REPUBLICA DEL JAPON</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5209,6 +5669,16 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
+          <t>5167 VICTOR RAUL HAYA DE LA TORRE/5167 VICTOR RAUL HAYA DE LA TORRE</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5312,6 +5782,16 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
+          <t>585 BELLA AURORA</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5415,6 +5895,16 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
+          <t>590 ESTRELLITA LUMINOSA</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5518,6 +6008,16 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
+          <t>331 DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5621,6 +6121,16 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
+          <t>JARDINES DE COPACABANA I</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5722,6 +6232,16 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5825,6 +6345,16 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
+          <t>597 NUESTRO SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5928,6 +6458,16 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
+          <t>0348 SANTA LUISA</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6031,6 +6571,16 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
+          <t>3719 SANTISIMA TRINIDAD/3719 SANTISIMA TRINIDAD</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6132,6 +6682,16 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6235,6 +6795,16 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
+          <t>5171 TUPAC AMARU II/5171 TUPAC AMARU II</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6336,6 +6906,16 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
+          <t>603 LOS NIÑOS DEL SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6439,6 +7019,16 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
+          <t>588 EMILIA BARCIA BONIFFATTI</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6540,6 +7130,16 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6643,6 +7243,16 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
+          <t>605 KUMAMOTO II</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6746,6 +7356,16 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
+          <t>6019 MARIANO MELGAR/6019 MARIANO MELGAR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6849,6 +7469,16 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
+          <t>6014/6014</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6950,6 +7580,16 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7053,6 +7693,16 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
+          <t>6084 SAN MARTIN DE PORRES/652 30/6084 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7156,6 +7806,16 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
+          <t>6057 VIRGEN DE LOURDES/6057 VIRGEN DE LOURDES/6057 VIRGEN DE LOURDES</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7259,6 +7919,16 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
+          <t>7094 SASAKAWA/7094 SASAKAWA/7094 SASAKAWA</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7362,6 +8032,16 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
+          <t>652 23 LOS PORTALES</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7465,6 +8145,16 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
+          <t>7233 MATSU UTSUMI/7233 MATSU UTSUMI/7233 MATSU UTSUMI</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7568,6 +8258,16 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
+          <t>652 20/6025</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7669,6 +8369,16 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7772,6 +8482,16 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
+          <t>018 OKINAWA</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7875,6 +8595,16 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
+          <t>JOSE ABELARDO QUIÑONEZ GONZALES/JOSE ABELARDO QUIÑONEZ GONZALES/JOSE ABELARDO QUIÑONEZ GONZALES</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7978,6 +8708,16 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
+          <t>2022 PEDRO ABRAHAM VALDELOMAR PINTO/2022 PEDRO ABRAHAM VALDELOMAR PINTO/2022 PEDRO ABRAHAM VALDELOMAR PINTO</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8081,6 +8821,16 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
+          <t>0001 NIÑO JESUS DE PRAGA</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8184,6 +8934,16 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
+          <t>0013 PASTORCITOS DE FATIMA</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8287,6 +9047,16 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
+          <t>2035 CARLOS CHIYOTERU HIRAOKA</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8388,6 +9158,16 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
+          <t>3047/3047</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8491,6 +9271,16 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
+          <t>2007 ROSA DE LAS AMERICAS/2007 ROSA DE LAS AMERICAS</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8594,6 +9384,16 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
+          <t>0022 SEMILLITAS DEL FUTURO</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8697,6 +9497,16 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
+          <t>0346 LAS PALMERAS</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8798,6 +9608,16 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
+          <t>2005 LOS OLIVOS/2005 LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8901,6 +9721,16 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
+          <t>PROYECTO INTEGRAL CHAVARRIA/PROYECTO INTEGRAL CHAVARRIA</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9004,6 +9834,16 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
+          <t>0351 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9107,6 +9947,16 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
+          <t>2090 VIRGEN DE LA PUERTA/2090 VIRGEN DE LA PUERTA/2090 VIRGEN DE LA PUERTA</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9210,6 +10060,16 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
+          <t>2037 SAN ANTONIO DE PADUA</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9313,6 +10173,16 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
+          <t>MANUEL GONZALES PRADA - CENTRO DE APLICACION/MANUEL GONZALES PRADA - CENTRO DE APLICACION</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9416,6 +10286,16 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
+          <t>7097 VILLA AMSTELVEEN/7097 VILLA AMSTELVEEN</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9519,6 +10399,16 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
+          <t>7091 REPUBLICA DEL PERU/7091 REPUBLICA DEL PERU/7091 REPUBLICA DEL PERU</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9622,6 +10512,16 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
+          <t>526 SANTISIMA VIRGEN DEL PERPETUO SOCORRO</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9725,6 +10625,16 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
+          <t>652 02 SANTA ROSA DE LIMA</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9826,6 +10736,16 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
+          <t>1224/1224/1224</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9929,6 +10849,16 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
+          <t>PADRE MIGUEL MARINA</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10032,6 +10962,16 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
+          <t>1233 MANUEL FERNANDO CABREL NICHO/1233 MANUEL FERNANDO CABREL NICHO/1233 MANUEL FERNANDO CABREL NICHO</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10133,6 +11073,16 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10234,6 +11184,16 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
+          <t>1250/1250</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10337,6 +11297,16 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
+          <t>384 LOS AMIGUITOS</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10440,6 +11410,16 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
+          <t>315 LOS ANGELES Y MARIA</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10543,6 +11523,16 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
+          <t>8190 SOL NACIENTE/8190 SOL NACIENTE</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10644,6 +11634,16 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10747,6 +11747,16 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
+          <t>865 CAUDEVILLA</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10850,6 +11860,16 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
+          <t>368 ANGELITOS DE JESUS</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10953,6 +11973,16 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
+          <t>8181 HEROES DEL ALTO CENEPA/8181 HEROES DEL ALTO CENEPA</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11056,6 +12086,16 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
+          <t>8156 PERUANO ALEMAN</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11159,6 +12199,16 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
+          <t>02 JOSE GALVITO</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11262,6 +12312,16 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
+          <t>8170 CESAR VALLEJO/8170 CESAR VALLEJO/8170 CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11365,6 +12425,16 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
+          <t>2035 FERNANDO BELAUNDE TERRY</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11466,6 +12536,16 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11567,6 +12647,16 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11670,6 +12760,16 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
+          <t>LUIS ENRIQUE XVII</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11771,6 +12871,16 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11872,6 +12982,16 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
+          <t>8162</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11975,6 +13095,16 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
+          <t>337 SANGARARA</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12078,6 +13208,16 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
+          <t>326 MARIA MONTESSORI</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12181,6 +13321,16 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
+          <t>3062 SANTA ROSA/3062 SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12282,6 +13432,16 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
+          <t>0009</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12385,6 +13545,16 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
+          <t>0386 VICTOR RAUL HAYA DE LA TORRE</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12488,6 +13658,16 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
+          <t>2058 VIRGEN DE LA MEDALLA MILAGROSA/2058 VIRGEN DE LA MEDALLA MILAGROSA</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12591,6 +13771,16 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
+          <t>2036 MARIA AUXILIADORA/2036 MARIA AUXILIADORA</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12694,6 +13884,16 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
+          <t>2053 FRANCISCO BOLOGNESI CERVANTES/2053 FRANCISCO BOLOGNESI CERVANTES/2053 FRANCISCO BOLOGNESI CERVANTES</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12797,6 +13997,16 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
+          <t>2039 JORGE VICTOR CASTILLA MONTERO/2039 JORGE VICTOR CASTILLA MONTERO</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12900,6 +14110,16 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
+          <t>0093 FERNANDO BELAUNDE TERRY</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13003,6 +14223,16 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
+          <t>LA PRADERA II/LA PRADERA II</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13106,6 +14336,16 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
+          <t>0085 JOSE DE LA TORRE UGARTE/0085 JOSE DE LA TORRE UGARTE/0085 JOSE DE LA TORRE UGARTE</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13209,6 +14449,16 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
+          <t>0086 CAMPOY</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13312,6 +14562,16 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
+          <t>SAN MATIAS DE JESUS/SAN MATIAS DE JESUS</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13415,6 +14675,16 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
+          <t>1186 SANTA ROSA DE LIMA MILAGROSA/1186 SANTA ROSA DE LIMA MILAGROSA</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13518,6 +14788,16 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
+          <t>1044 MARIA REICHE NEWMANN/1044 MARIA REICHE NEWMANN/1044 MARIA REICHE NEWMANN</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13621,6 +14901,16 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
+          <t>0049 ANTONIA MORENO DE CACERES/0049 ANTONIA MORENO DE CACERES</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13724,6 +15014,16 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
+          <t>HOGAR SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13827,6 +15127,16 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
+          <t>1128 SAN LUIS/1128 SAN LUIS/1128 SAN LUIS/1128 SAN LUIS</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13930,6 +15240,16 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
+          <t>RICARDO BENTIN/RICARDO BENTIN/RICARDO BENTIN</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14033,6 +15353,16 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
+          <t>3006 JOSE ERNESTO ECHENIQUE RODRIGUEZ/3006 JOSE ERNESTO ECHENIQUE RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14134,6 +15464,16 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
+          <t>0320 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14237,6 +15577,16 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
+          <t>3010 RAMON CASTILLA/3010 RAMON CASTILLA</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14340,6 +15690,16 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
+          <t>391-1 FLOR DE AMANCAES</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14443,6 +15803,16 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
+          <t>1217 JORGE BASADRE/1217 JORGE BASADRE</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14546,6 +15916,16 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
+          <t>0108 SANTA ROSA DE QUIVES/0108 SANTA ROSA DE QUIVES</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14649,6 +16029,16 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
+          <t>1188 JUAN PABLO II/1188 JUAN PABLO II</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14752,6 +16142,16 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
+          <t>0124 GLORIOSA LEGION CACERES/0124 GLORIOSA LEGION CACERES/0124 GLORIOSA LEGION CACERES</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14853,6 +16253,16 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14956,6 +16366,16 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
+          <t>104 VIRGEN DE LA PUERTA</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15059,6 +16479,16 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
+          <t>1201 PAUL HARRIS/1201 PAUL HARRIS</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15162,6 +16592,16 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
+          <t>1117 ANDRES AVELINO ARAMBURU</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15265,6 +16705,16 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
+          <t>SANTA BERNARDITA</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15368,6 +16818,16 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
+          <t>005 JESUSITO MILAGROSO</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15471,6 +16931,16 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
+          <t>1124 JOSE MARTI/1124 JOSE MARTI</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15574,6 +17044,16 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
+          <t>020 MADRE TERESA DE CALCUTA/1120 PEDRO ADOLFO LABARTHE EFFIO/1120 PEDRO ADOLFO LABARTHE EFFIO/1120 PEDRO ADOLFO LABARTHE EFFIO/020 MADRE TERESA DE CALCUTA/1120 PEDRO ADOLFO LABARTHE EFFIO/1120 PEDRO ADOLFO LABARTHE EFFIO</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15677,6 +17157,16 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
+          <t>1105 LA SAGRADA FAMILIA/1105 LA SAGRADA FAMILIA/1105 LA SAGRADA FAMILIA</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15780,6 +17270,16 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
+          <t>501 MONSEÑOR DAMASO LEBERGERE/501 MONSEÑOR DAMASO LEBERGERE</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15883,6 +17383,16 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
+          <t>CESAR A. VALLEJO/CESAR A. VALLEJO/CESAR A. VALLEJO</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15986,6 +17496,16 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
+          <t>1003 REPUBLICA DE COLOMBIA/1003 REPUBLICA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16089,6 +17609,16 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
+          <t>1148 JUANA INFANTES VERA/1148 JUANA INFANTES VERA</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16192,6 +17722,16 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
+          <t>1021 REPUBLICA FEDERAL DE ALEMANIA/1021 REPUBLICA FEDERAL DE ALEMANIA</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16293,6 +17833,16 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
+          <t>1161/1161</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16396,6 +17946,16 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
+          <t>172 JOSE LUIS BUSTAMANTE Y RIVERO</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16499,6 +18059,16 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
+          <t>1162 DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16602,6 +18172,16 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
+          <t>1146 REPUBLICA DEL PARAGUAY/1146 REPUBLICA DEL PARAGUAY/1146 REPUBLICA DEL PARAGUAY</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16705,6 +18285,16 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
+          <t>1160 JOSE FAUSTINO SANCHEZ CARRION/1160 JOSE FAUSTINO SANCHEZ CARRION</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16808,6 +18398,16 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
+          <t>JARDIN DE LA INFANCIA N 1 DE LIMA</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16911,6 +18511,16 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
+          <t>1087 GRAL ROQUE SAENZ PEÑA/1087 GRAL ROQUE SAENZ PEÑA/1087 GRAL ROQUE SAENZ PEÑA</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17014,6 +18624,16 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
+          <t>111 SAN JOSE DE ARTESANOS/111 SAN JOSE DE ARTESANOS/111 SAN JOSE DE ARTESANOS</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17117,6 +18737,16 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
+          <t>030 SANTA TERESITA DEL DIVINO NIÑO</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17220,6 +18850,16 @@
       </c>
       <c r="U164" t="inlineStr">
         <is>
+          <t>1048 VIRGEN PURISIMA</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17323,6 +18963,16 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
+          <t>077 MANZANILLA</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17426,6 +19076,16 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
+          <t>022 REPUBLICA DE GUATEMALA/022 REPUBLICA DE GUATEMALA/022 REPUBLICA DE GUATEMALA</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17527,6 +19187,16 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
+          <t>5087</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17630,6 +19300,16 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
+          <t>ESCUELA HOGAR COMUNITARIA REGIONAL SAGRADA FAMILIA/ESCUELA HOGAR COMUNITARIA REGIONAL SAGRADA FAMILIA/ESCUELA HOGAR COMUNITARIA REGIONAL SAGRADA FAMILIA</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17733,6 +19413,16 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
+          <t>123 VIRGEN DE LA ASUNCION</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17836,6 +19526,16 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
+          <t>120 LAS CASUARINAS</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17939,6 +19639,16 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
+          <t>130 VIDA Y ALEGRIA</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18042,6 +19752,16 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
+          <t>5116 DIVINO CREADOR</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18145,6 +19865,16 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
+          <t>5135 LA SALLE/5135 LA SALLE/5135 LA SALLE</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18248,6 +19978,16 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
+          <t>5141 DIVINO MAESTRO/5141 DIVINO MAESTRO/5141 DIVINO MAESTRO</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18351,6 +20091,16 @@
       </c>
       <c r="U175" t="inlineStr">
         <is>
+          <t>99 CORAZON DE MARIA</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18454,6 +20204,16 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
+          <t>5148 LAS BRISAS DE PACHACUTEC/5148 LAS BRISAS DE PACHACUTEC</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18555,6 +20315,16 @@
       </c>
       <c r="U177" t="inlineStr">
         <is>
+          <t>5146/5146</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18656,6 +20426,16 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18759,6 +20539,16 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
+          <t>125 DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18858,6 +20648,16 @@
       </c>
       <c r="U180" t="inlineStr">
         <is>
+          <t>5117 JORGE PORTOCARRERO REBAZA</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18959,6 +20759,16 @@
       </c>
       <c r="U181" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19062,6 +20872,16 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
+          <t>5090 ANTONIA MORENO DE CACERES/5090 ANTONIA MORENO DE CACERES</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19163,6 +20983,16 @@
       </c>
       <c r="U183" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19264,6 +21094,16 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19365,6 +21205,16 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19466,6 +21316,16 @@
       </c>
       <c r="U186" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19569,6 +21429,16 @@
       </c>
       <c r="U187" t="inlineStr">
         <is>
+          <t>85 NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19672,6 +21542,16 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
+          <t>073 SEÑOR DE LA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19775,6 +21655,16 @@
       </c>
       <c r="U189" t="inlineStr">
         <is>
+          <t>80 LOS NIÑOS DE JESUS</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19878,6 +21768,16 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
+          <t>82 PASTORCITOS DE OQUENDO</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19981,6 +21881,16 @@
       </c>
       <c r="U191" t="inlineStr">
         <is>
+          <t>109 DIVINO JESUS</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20084,6 +21994,16 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
+          <t>76 MI AMIGO JESUS</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20187,6 +22107,16 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
+          <t>071 RETOÑITOS DE LA VIRGEN DE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20290,6 +22220,16 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
+          <t>78 AMIGUITOS DE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20393,6 +22333,16 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
+          <t>79 ANGELES DE SARITA</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20496,6 +22446,16 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
+          <t>5043 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20599,6 +22559,16 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
+          <t>5040 PEDRO RUIZ/5040 PEDRO RUIZ</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20702,6 +22672,16 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
+          <t>62 PASITOS DE JESUS</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20805,6 +22785,16 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
+          <t>5003 VIRGEN DE LA INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20908,6 +22898,16 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
+          <t>5007 NUESTRA SEÑORA DE GUADALUPE/5007 NUESTRA SEÑORA DE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -21010,6 +23010,16 @@
         </is>
       </c>
       <c r="U201" t="inlineStr">
+        <is>
+          <t>4001 DOS DE MAYO/4001 DOS DE MAYO/4001 DOS DE MAYO/4001 DOS DE MAYO/4001 DOS DE MAYO</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
         <is>
           <t>FONCODES</t>
         </is>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2025.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2025.xlsx
@@ -419,62 +419,62 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CODIGO MODULAR</t>
+          <t>cod_mod</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>PROVINCIA</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>DISTRITO</t>
+          <t>distrito</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>NOMBRE IE</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>TIPO DE MANTENIMIENTO</t>
+          <t>tipo_de_mantenimiento</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>MONTO DE LA INTERVENCIÓN 2025</t>
+          <t>monto_de_la_intervencion_2025</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>% AVANCE</t>
+          <t>avance</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ESTADO PROYECTO</t>
+          <t>estado_proyecto</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>FECHA DE INICIO</t>
+          <t>fecha_de_inicio</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>FECHA DE CULMINACIÓN</t>
+          <t>fecha_de_culminacion</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -484,17 +484,17 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>departamento</t>
+          <t>departamento_2</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>provincia</t>
+          <t>provincia_2</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>distrito</t>
+          <t>distrito_2</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
